--- a/shared/reidentificacion.xlsx
+++ b/shared/reidentificacion.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -855,6 +855,56 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>pagos_yape_tepago.xlsx (archivo 2026-07) / ReporteTransacciones+51948227636.xlsx</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>15</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Irma Huanahui Lopez (C-13, U0045) yapeo S/15 el 07/07 10:15:12 con mensaje 'mz.lt11' -- sin letra de manzana. El motor no pudo parsear el mensaje y cayo por default al maestro (ella misma, C-13), en vez de mandarlo a revision. El '11' del mensaje es K-11 (Martina Morales Rios, U0203), reclamo confirmado por la secretaria (cuaderno papel, Reclamos agosto). K-11 tenia MES_ANTERIOR=15 exacto en planilla de agosto -- coincide al centavo. El otro balde de la misma corrida de Irma (S/50, tanque) va en aportes_tanque_manuales.xlsx, mismo ancla. Se aplica en 2026-08 porque julio ya esta cerrado y es cuando el credito de K-11 aparece vigente en planilla_cobrado.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>reclamos_manuales.xlsx fila K-11 (2026-08-10)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
